--- a/artfynd/A 47596-2025 artfynd.xlsx
+++ b/artfynd/A 47596-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>113679136</v>
       </c>
       <c r="B2" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,12 +770,12 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>

--- a/artfynd/A 47596-2025 artfynd.xlsx
+++ b/artfynd/A 47596-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113679136</v>
       </c>
       <c r="B2" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47596-2025 artfynd.xlsx
+++ b/artfynd/A 47596-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113679136</v>
       </c>
       <c r="B2" t="n">
-        <v>80422</v>
+        <v>80424</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47596-2025 artfynd.xlsx
+++ b/artfynd/A 47596-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113679136</v>
       </c>
       <c r="B2" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
